--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.52687040924647</v>
+        <v>3.010616441502551</v>
       </c>
       <c r="D2" t="n">
-        <v>20.18075591184794</v>
+        <v>3.27937283567529</v>
       </c>
       <c r="E2" t="n">
-        <v>23.59613725516882</v>
+        <v>3.834372303964934</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1339810854804</v>
+        <v>1.971771926390565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.22917706323173</v>
+        <v>12.71224127277516</v>
       </c>
       <c r="D3" t="n">
-        <v>22.2485101131951</v>
+        <v>3.615382893394203</v>
       </c>
       <c r="E3" t="n">
-        <v>23.59613725516882</v>
+        <v>3.834372303964934</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1339810854804</v>
+        <v>1.971771926390565</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.20519553117645</v>
+        <v>8.483344273816174</v>
       </c>
       <c r="D4" t="n">
-        <v>50.87924236069677</v>
+        <v>8.267876883613226</v>
       </c>
       <c r="E4" t="n">
-        <v>23.59613725516882</v>
+        <v>3.834372303964934</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1339810854804</v>
+        <v>1.971771926390565</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.56604031172013</v>
+        <v>4.154481550654522</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67572330035593</v>
+        <v>4.984805036307839</v>
       </c>
       <c r="E5" t="n">
-        <v>23.59613725516882</v>
+        <v>3.834372303964934</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1339810854804</v>
+        <v>1.971771926390565</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
